--- a/data/gated_research/model_ledgers/rainbow-six-tiered-elo.xlsx
+++ b/data/gated_research/model_ledgers/rainbow-six-tiered-elo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Predictions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Predictions'!$A$1:$AJ$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -433,7 +433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ3"/>
+  <dimension ref="A1:AJ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -860,8 +860,1150 @@
       <c r="AI3" s="2" t="inlineStr"/>
       <c r="AJ3" s="2" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>ecdd96410dbd4813</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3b81c1a225385446e6c2efcb53bbcef49ca7c03c0ccb69faec9e458b1a6f00c1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>75283</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0.582007</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" s="2" t="inlineStr"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0.3802281368821293</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr"/>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>0.20177886311787074</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T14:01:43.349448Z</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr"/>
+      <c r="U4" s="2" t="inlineStr"/>
+      <c r="V4" s="2" t="inlineStr"/>
+      <c r="W4" s="2" t="inlineStr"/>
+      <c r="X4" s="2" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
+        <is>
+          <t>0.360000</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
+          <t>-0.020228</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>2.0375</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:05:20.229398Z</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>67409f98aff84b1a</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>e83a3ac7069db9030b6e73562e1d182c7126691e9608825d6879cd3d08d6102b</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>76934</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0.63019</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr"/>
+      <c r="N5" s="2" t="inlineStr"/>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>0.6000000000000001</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr"/>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>0.03018999999999994</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11T19:58:25.883751Z</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr"/>
+      <c r="U5" s="2" t="inlineStr"/>
+      <c r="V5" s="2" t="inlineStr"/>
+      <c r="W5" s="2" t="inlineStr"/>
+      <c r="X5" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr"/>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>9b82111b53e049ba</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>683507eb972ca2dde1f3ed76f99a039559c55d63946164b3366f174f8e38632a</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>76934</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0.630084</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>0.609375</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr"/>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>0.020708999999999977</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-11T23:03:46.758426Z</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr"/>
+      <c r="V6" s="2" t="inlineStr"/>
+      <c r="W6" s="2" t="inlineStr"/>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr"/>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>65de2847118e4cf3</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5927380effc0fd200d8f5ee707e04a74e0ab76a027aecbe00226842cba129b19</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>76934</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0.629976</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr"/>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>0.5901639344262295</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr"/>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>0.03981206557377048</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T02:10:02.145114Z</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr"/>
+      <c r="V7" s="2" t="inlineStr"/>
+      <c r="W7" s="2" t="inlineStr"/>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>126d746efbe446a0</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>a247738f7e3a05afd3824b27a7df4c07a881cca13a81c1e3a5155a97c016e160</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>77319</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0.645071</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>0.02529913688212926</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:16:08.793606Z</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr"/>
+      <c r="V8" s="2" t="inlineStr"/>
+      <c r="W8" s="2" t="inlineStr"/>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>f0c6332678cf4cc6</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>a247738f7e3a05afd3824b27a7df4c07a881cca13a81c1e3a5155a97c016e160</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0.740676</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>0.6402877697841727</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr"/>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>0.10038823021582732</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T05:16:09.447658Z</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr"/>
+      <c r="V9" s="2" t="inlineStr"/>
+      <c r="W9" s="2" t="inlineStr"/>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr"/>
+      <c r="AI9" s="2" t="inlineStr"/>
+      <c r="AJ9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>3dd9b3aef96b4494</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6f58fd90e08e64d0a58042eeb19a26a1debe889dbb200a082a99f51d84977c3b</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>77319</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0.644944</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>0.02517213688212927</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:22:24.701853Z</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T14:00:00Z</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr"/>
+      <c r="V10" s="2" t="inlineStr"/>
+      <c r="W10" s="2" t="inlineStr"/>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr"/>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr"/>
+      <c r="AI10" s="2" t="inlineStr"/>
+      <c r="AJ10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>5d17ff3d6d634a11</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>6f58fd90e08e64d0a58042eeb19a26a1debe889dbb200a082a99f51d84977c3b</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>0.740471</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr"/>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>0.11084137037037045</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T08:22:25.426868Z</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr"/>
+      <c r="V11" s="2" t="inlineStr"/>
+      <c r="W11" s="2" t="inlineStr"/>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr"/>
+      <c r="AI11" s="2" t="inlineStr"/>
+      <c r="AJ11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>7da8b092dc104ad5</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7374b813c568939dd2dea90ed4c12ad78e24834117de140d0ad4d70bf9edd602</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0.740265</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr"/>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>0.6296296296296295</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr"/>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>0.11063537037037041</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T11:30:04.536403Z</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr"/>
+      <c r="V12" s="2" t="inlineStr"/>
+      <c r="W12" s="2" t="inlineStr"/>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr"/>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr"/>
+      <c r="AI12" s="2" t="inlineStr"/>
+      <c r="AJ12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>e14045d560dc412c</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>ff702d2b685aebbdebd0127911b99b1822bd9d311c75192655ecfe2c55fcb8bc</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>0.74006</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr"/>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr"/>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>0.12028813688212936</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T14:37:10.720917Z</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr"/>
+      <c r="V13" s="2" t="inlineStr"/>
+      <c r="W13" s="2" t="inlineStr"/>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr"/>
+      <c r="AI13" s="2" t="inlineStr"/>
+      <c r="AJ13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>a0da5c85be384ddb</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>rainbow-six-tiered-elo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>815cb088e917b6a7c0f8a38d775d446292769b4ccda7155204e46f86c22c3711</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0.73992</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0.6197718631178707</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr"/>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>0.12014813688212933</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-12T16:44:43.930162Z</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr"/>
+      <c r="V14" s="2" t="inlineStr"/>
+      <c r="W14" s="2" t="inlineStr"/>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr"/>
+      <c r="AI14" s="2" t="inlineStr"/>
+      <c r="AJ14" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AJ3"/>
+  <autoFilter ref="A1:AJ14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>